--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-protocols-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-protocols-easy.xlsx
@@ -460,19 +460,19 @@
         <v>UART là giao thức truyền thông bất đồng bộ nối tiếp, sử dụng dây Tx của thiết bị này nối với dây Rx của thiết bị kia và ngược lại, bắt buộc phải nối chung chân đất GND.</v>
       </c>
       <c r="F2" t="str">
+        <v>1 dây tín hiệu duy nhất không cần dây đất — giao thức 1-Wire</v>
+      </c>
+      <c r="G2" t="str">
         <v>2 dây: Tx (Truyền) và Rx (Nhận), dùng chung dây nối đất GND — 2 dây tín hiệu Tx Rx</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>3 dây: SDA, SCL và GND — giao thức I2C</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>4 dây: MISO, MOSI, SCK và SS — giao thức SPI</v>
       </c>
-      <c r="I2" t="str">
-        <v>1 dây tín hiệu duy nhất không cần dây đất — giao thức 1-Wire</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Vì không có dây Clock dùng chung, hai thiết bị giao tiếp UART (bất đồng bộ) phải được cấu hình sẵn cùng một tốc độ truyền nhận (Baudrate) và cấu hình khung truyền (Start bit, Stop bit, Parity).</v>
       </c>
       <c r="F3" t="str">
+        <v>Bất đồng bộ chỉ truyền được dữ liệu dạng hình ảnh; còn đồng bộ chỉ truyền được dữ liệu số — loại dữ liệu truyền</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Bất đồng bộ có tốc độ truyền tải nhanh gấp 100 lần so với giao tiếp đồng bộ — tốc độ truyền tải</v>
+      </c>
+      <c r="H3" t="str">
         <v>Bất đồng bộ không sử dụng dây xung nhịp Clock (CLK) dùng chung; đồng bộ bắt buộc phải có dây Clock để đồng bộ hóa bit dữ liệu — không có dây Clock vs có dây Clock</v>
       </c>
-      <c r="G3" t="str">
-        <v>Bất đồng bộ chỉ truyền được dữ liệu dạng hình ảnh; còn đồng bộ chỉ truyền được dữ liệu số — loại dữ liệu truyền</v>
-      </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Bất đồng bộ bắt buộc phải chạy trên hệ điều hành RTOS; còn đồng bộ chạy Bare-metal — môi trường chạy phần mềm</v>
       </c>
-      <c r="I3" t="str">
-        <v>Bất đồng bộ có tốc độ truyền tải nhanh gấp 100 lần so với giao tiếp đồng bộ — tốc độ truyền tải</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>I2C là giao thức truyền thông nối tiếp đồng bộ, sử dụng 2 dây: SDA truyền nhận dữ liệu, SCL cấp xung nhịp clock đồng bộ.</v>
       </c>
       <c r="F4" t="str">
+        <v>CAN_H và CAN_L — giao thức CAN Bus</v>
+      </c>
+      <c r="G4" t="str">
+        <v>MOSI, MISO và SCK — giao thức SPI</v>
+      </c>
+      <c r="H4" t="str">
         <v>SDA (Dữ liệu nối tiếp) và SCL (Xung nhịp nối tiếp) — 2 dây Bus chung</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Tx và Rx — giao thức UART</v>
       </c>
-      <c r="H4" t="str">
-        <v>MOSI, MISO và SCK — giao thức SPI</v>
-      </c>
-      <c r="I4" t="str">
-        <v>CAN_H và CAN_L — giao thức CAN Bus</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Cấu trúc Open-drain của I2C cho phép nhiều thiết bị nối chung đường bus mà không lo chập mạch khi thiết bị này kéo bus xuống đất (Low) và thiết bị kia đẩy lên cao (High). Khi không có thiết bị nào kéo bus xuống đất, điện trở pull-up sẽ duy trì điện áp bus ở mức cao (High).</v>
       </c>
       <c r="F5" t="str">
+        <v>Để giảm thiểu dòng điện tiêu thụ của vi điều khiển xuống bằng 0 — tiết kiệm điện năng</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Để lọc các nhiễu sóng cao tần phát ra từ các thiết bị thu phát Wi-Fi bên ngoài — lọc nhiễu sóng</v>
+      </c>
+      <c r="H5" t="str">
         <v>Vì các chân I2C cấu hình ở dạng cực máng hở (Open-drain), điện trở kéo lên giúp kéo điện áp đường bus lên mức cao (Logical 1) khi bus rảnh — điện trở kéo lên cho cực máng hở Open-drain</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Để giảm thiểu dòng điện tiêu thụ của vi điều khiển xuống bằng 0 — tiết kiệm điện năng</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Để lọc các nhiễu sóng cao tần phát ra từ các thiết bị thu phát Wi-Fi bên ngoài — lọc nhiễu sóng</v>
       </c>
       <c r="I5" t="str">
         <v>Vì nếu không có điện trở, vi điều khiển sẽ bị cháy chip do hiện tượng đoản mạch phần cứng — bảo vệ đoản mạch</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -594,10 +594,10 @@
         <v>2 dây: SDA và SCL — giao thức I2C</v>
       </c>
       <c r="H6" t="str">
+        <v>2 dây: CAN_H và CAN_L — giao thức CAN Bus</v>
+      </c>
+      <c r="I6" t="str">
         <v>2 dây: Tx và Rx — giao thức UART</v>
-      </c>
-      <c r="I6" t="str">
-        <v>2 dây: CAN_H và CAN_L — giao thức CAN Bus</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -620,19 +620,19 @@
         <v>Khi Master muốn giao tiếp với Slave nào (trong mô hình nhiều Slave dùng chung bus SPI), Master sẽ kéo chân CS của Slave đó xuống mức thấp (Active Low) để đánh thức nó.</v>
       </c>
       <c r="F7" t="str">
-        <v>Được Master kéo xuống mức thấp (Low) để kích hoạt và lựa chọn chip Slave cụ thể muốn giao tiếp — chọn chip Slave tương tác</v>
+        <v>Tự động reset lại chip Slave khi phát sinh lỗi truyền dẫn dữ liệu — reset chip Slave</v>
       </c>
       <c r="G7" t="str">
         <v>Cấp nguồn điện 3.3V trực tiếp cho các linh kiện ngoại vi hoạt động — cấp nguồn điện vật lý</v>
       </c>
       <c r="H7" t="str">
+        <v>Được Master kéo xuống mức thấp (Low) để kích hoạt và lựa chọn chip Slave cụ thể muốn giao tiếp — chọn chip Slave tương tác</v>
+      </c>
+      <c r="I7" t="str">
         <v>Truyền nhận các mã lệnh điều khiển tốc độ xung nhịp của vi điều khiển — điều khiển xung nhịp clock</v>
       </c>
-      <c r="I7" t="str">
-        <v>Tự động reset lại chip Slave khi phát sinh lỗi truyền dẫn dữ liệu — reset chip Slave</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Baudrate (ví dụ: 9600 bps, 115200 bps) là đơn vị đo tốc độ truyền thông nối tiếp, thể hiện số lượng đơn vị tín hiệu (bit) truyền đi trên đường dây trong 1 giây.</v>
       </c>
       <c r="F8" t="str">
+        <v>Số byte dữ liệu tối đa bộ đệm UART có thể chứa — dung lượng bộ đệm</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Thời gian trễ tính bằng mili-giây từ khi gửi đến khi nhận dữ liệu — độ trễ truyền dữ liệu</v>
+      </c>
+      <c r="H8" t="str">
         <v>Số lượng bit dữ liệu được truyền đi thành công trong một giây (bits per second) — tốc độ bit truyền nhận</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Số byte dữ liệu tối đa bộ đệm UART có thể chứa — dung lượng bộ đệm</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Thời gian trễ tính bằng mili-giây từ khi gửi đến khi nhận dữ liệu — độ trễ truyền dữ liệu</v>
       </c>
       <c r="I8" t="str">
         <v>Tần số dao động của bộ thạch anh nội vi của vi điều khiển — tần số thạch anh chip</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>I2C là giao thức định địa chỉ bằng phần mềm (Software Addressing). Mỗi Slave có một địa chỉ cố định. Khi bắt đầu khung truyền (Start condition), Master sẽ gửi địa chỉ Slave đó lên bus, các Slave khác đọc thấy không phải địa chỉ của mình sẽ bỏ qua.</v>
       </c>
       <c r="F9" t="str">
+        <v>Master bắt buộc phải gửi tin nhắn văn bản tiếng Việt yêu cầu Slave thức dậy — gửi tin nhắn văn bản</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Các Slave tự động chia ca hoạt động luân phiên theo thời gian thực — chia ca hoạt động</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Master kéo chân CS vật lý của Slave đó xuống đất — cơ chế CS của SPI</v>
+      </c>
+      <c r="I9" t="str">
         <v>Master gửi một khung truyền chứa địa chỉ vật lý duy nhất (Address - 7 bit hoặc 10 bit) của Slave đó lên bus — địa chỉ vật lý duy nhất của Slave</v>
       </c>
-      <c r="G9" t="str">
-        <v>Master kéo chân CS vật lý của Slave đó xuống đất — cơ chế CS của SPI</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Master bắt buộc phải gửi tin nhắn văn bản tiếng Việt yêu cầu Slave thức dậy — gửi tin nhắn văn bản</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Các Slave tự động chia ca hoạt động luân phiên theo thời gian thực — chia ca hoạt động</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>SPI là ví dụ điển hình của Full-duplex: có đường truyền MOSI và đường nhận MISO riêng biệt chạy đồng thời theo xung nhịp clock. UART cũng là Full-duplex nhờ dây Tx và Rx độc lập. I2C là Half-duplex do chỉ dùng chung 1 dây dữ liệu SDA.</v>
       </c>
       <c r="F10" t="str">
+        <v>Thiết bị bắt buộc phải sử dụng nguồn điện kép 5V và 12V cùng lúc khi hoạt động — nguồn điện kép</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Hệ thống cho phép truyền dữ liệu cả hai chiều nhưng tại một thời điểm chỉ được phép truyền hoặc nhận — bán song công Half-duplex</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Thiết bị chỉ có thể truyền dữ liệu đi chứ không thể nhận dữ liệu về — truyền một chiều Simplex</v>
+      </c>
+      <c r="I10" t="str">
         <v>Thiết bị có thể thực hiện việc truyền (Transmit) và nhận (Receive) dữ liệu hoàn toàn song song và đồng thời — truyền nhận song song đồng thời</v>
       </c>
-      <c r="G10" t="str">
-        <v>Thiết bị chỉ có thể truyền dữ liệu đi chứ không thể nhận dữ liệu về — truyền một chiều Simplex</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Hệ thống cho phép truyền dữ liệu cả hai chiều nhưng tại một thời điểm chỉ được phép truyền hoặc nhận — bán song công Half-duplex</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Thiết bị bắt buộc phải sử dụng nguồn điện kép 5V và 12V cùng lúc khi hoạt động — nguồn điện kép</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>CAN Bus được phát triển bởi Bosch, là giao thức truyền thông mạnh mẽ, chống nhiễu cực tốt, kết nối các ECU trên ô tô thông qua mạng dây vi sai.</v>
       </c>
       <c r="F11" t="str">
-        <v>Ngành công nghiệp ô tô (Automotive) để kết nối các hộp điều khiển ECU trên xe hơi — truyền thông xe hơi</v>
+        <v>Ngành công nghiệp thiết kế trò chơi điện tử trực tuyến chạy trên PC — đồ họa game</v>
       </c>
       <c r="G11" t="str">
-        <v>Ngành công nghiệp thiết kế trò chơi điện tử trực tuyến chạy trên PC — đồ họa game</v>
+        <v>Ngành ngân hàng để thực hiện các giao dịch chuyển tiền trực tuyến xuyên quốc gia — tài chính ngân hàng</v>
       </c>
       <c r="H11" t="str">
         <v>Ngành y tế để thiết kế các phần mềm quản lý hồ sơ bệnh án của bệnh nhân — quản lý bệnh viện</v>
       </c>
       <c r="I11" t="str">
-        <v>Ngành ngân hàng để thực hiện các giao dịch chuyển tiền trực tuyến xuyên quốc gia — tài chính ngân hàng</v>
+        <v>Ngành công nghiệp ô tô (Automotive) để kết nối các hộp điều khiển ECU trên xe hơi — truyền thông xe hơi</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
